--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.1.xlsx
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -737,13 +737,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -772,6 +775,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -844,6 +848,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1046,6 +1051,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="15" t="inlineStr">
         <is>
@@ -1053,6 +1059,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="16" t="inlineStr">
         <is>
@@ -1179,6 +1186,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -2327,6 +2335,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -3431,6 +3440,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -4862,6 +4872,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -5209,6 +5220,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -7355,6 +7367,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -7939,6 +7952,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -8928,6 +8942,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -10606,6 +10621,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -11648,6 +11664,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -13232,7 +13249,7 @@
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>Please name the recipients of the operational notices: failed batch runs (BRD p.15; parameter job failure recipients, empty as delivered), the privileged-change alert, the summary of dormant-user deactivations, and any unit mailbox that must receive access-change notices besides the users concerned..</t>
+          <t>Please name the recipients of the operational notices: failed batch runs (BRD p.15; parameter job failure recipients, empty by default), the privileged-change alert, the summary of dormant-user deactivations, and any unit mailbox that must receive access-change notices besides the users concerned..</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
@@ -13379,6 +13396,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -14156,6 +14174,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -14680,7 +14699,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Please complete the role-to-permission matrix (template CI-02): the group profiles BDOI keeps and the permissions of each, starting from the User Access Matrix as delivered..</t>
+          <t>Please complete the role-to-permission matrix (template CI-02): the group profiles BDOI keeps and the permissions of each, starting from the User Access Matrix by default..</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.1.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_Inputs_BRD-11_Business_Unit_Requirements_Collection_v1.1.xlsx
@@ -25,6 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$119</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Start here'!$A$4:$I$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Start here'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Documents and print formats'!$A$12:$K$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
@@ -1086,7 +1087,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2236,7 +2237,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3341,7 +3342,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4777,7 +4778,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5105,7 +5106,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5181,7 +5182,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7323,7 +7324,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7829,6 +7830,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:I14"/>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
@@ -7853,7 +7855,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -8843,7 +8845,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -10522,7 +10524,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -11565,7 +11567,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -13297,7 +13299,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -14075,7 +14077,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -15065,7 +15067,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.1</oddFooter>
     <evenHeader/>
     <evenFooter/>
